--- a/registration_forms/039_exam_fees_payment_form--registration_forms.xlsx
+++ b/registration_forms/039_exam_fees_payment_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1129,8 +1129,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'card_number'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'Label': 'Card Number'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Label': 'Bank Transfer'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'check'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Label': 'Check'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'paid'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'Label': 'Paid'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'Label': 'Pending'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'failed'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'Label': 'Failed'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'theory'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'Label': 'Theory'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'practical'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'Label': 'Practical'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'Label': 'Morning'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'Label': 'Afternoon'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'session_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'Label': 'Session 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'session_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'Label': 'Session 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'card_number'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'Label': 'Card Number'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'Label': 'Bank Transfer'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'check'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'Label': 'Check'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'stripe'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'Label': 'Stripe'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'Label': 'PayPal'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
